--- a/main/ig/StructureDefinition-fr-lm-reference-item-plan-traitement.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-reference-item-plan-traitement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-25T10:05:30+00:00</t>
+    <t>2026-03-13T14:11:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-reference-item-plan-traitement.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-reference-item-plan-traitement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T14:11:35+00:00</t>
+    <t>2026-03-13T17:00:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-reference-item-plan-traitement.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-reference-item-plan-traitement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T17:00:40+00:00</t>
+    <t>2026-03-13T17:26:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-reference-item-plan-traitement.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-reference-item-plan-traitement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T17:26:39+00:00</t>
+    <t>2026-03-13T17:26:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-reference-item-plan-traitement.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-reference-item-plan-traitement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T17:26:16+00:00</t>
+    <t>2026-03-13T22:26:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-reference-item-plan-traitement.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-reference-item-plan-traitement.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.1.0-snapsnot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T22:26:12+00:00</t>
+    <t>2026-03-20T08:18:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-reference-item-plan-traitement.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-reference-item-plan-traitement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T08:18:16+00:00</t>
+    <t>2026-03-23T13:14:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-reference-item-plan-traitement.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-reference-item-plan-traitement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-23T13:14:10+00:00</t>
+    <t>2026-03-27T09:33:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-reference-item-plan-traitement.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-reference-item-plan-traitement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T09:33:49+00:00</t>
+    <t>2026-03-30T15:11:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-reference-item-plan-traitement.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-reference-item-plan-traitement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T15:11:58+00:00</t>
+    <t>2026-03-31T07:16:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
